--- a/import-files/Lower Placement Logs.xlsx
+++ b/import-files/Lower Placement Logs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1BFE6D-CE93-4C42-8876-103720E552C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B51DDE-F233-41AA-95DA-B3321AC92E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>Pts</t>
   </si>
   <si>
-    <t>BOO 3</t>
-  </si>
-  <si>
     <t>Lower</t>
   </si>
   <si>
@@ -110,18 +107,9 @@
     <t>West Point 2</t>
   </si>
   <si>
-    <t>SEAGULLS 2</t>
-  </si>
-  <si>
     <t>Cathkin 2</t>
   </si>
   <si>
-    <t>SEAGULLS 1</t>
-  </si>
-  <si>
-    <t>BOO 4</t>
-  </si>
-  <si>
     <t>East Side 1</t>
   </si>
   <si>
@@ -135,6 +123,18 @@
   </si>
   <si>
     <t>Cathkin 3</t>
+  </si>
+  <si>
+    <t>Seagulls 1</t>
+  </si>
+  <si>
+    <t>Seagulls 2</t>
+  </si>
+  <si>
+    <t>Boo 3</t>
+  </si>
+  <si>
+    <t>Boo 4</t>
   </si>
 </sst>
 </file>
@@ -695,49 +695,49 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>20</v>
-      </c>
       <c r="D2" s="9">
-        <v>47287</v>
+        <v>55161</v>
       </c>
       <c r="E2" s="9">
-        <v>2861</v>
+        <v>3300</v>
       </c>
       <c r="F2" s="10">
-        <v>49.584411045089126</v>
+        <v>50.146363636363631</v>
       </c>
       <c r="G2" s="9">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="H2" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="9">
         <v>0</v>
       </c>
       <c r="J2" s="9">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K2" s="9">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L2" s="9">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N2" s="11">
-        <v>0.73958333333333337</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="O2" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q2" s="9">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
@@ -754,49 +754,49 @@
         <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="9">
-        <v>46594</v>
+        <v>54463</v>
       </c>
       <c r="E3" s="9">
-        <v>2960</v>
+        <v>3424</v>
       </c>
       <c r="F3" s="10">
-        <v>47.223648648648648</v>
+        <v>47.71875</v>
       </c>
       <c r="G3" s="9">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H3" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="9">
         <v>0</v>
       </c>
       <c r="J3" s="9">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K3" s="9">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="L3" s="9">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M3" s="9">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N3" s="11">
-        <v>0.61458333333333337</v>
+        <v>0.6339285714285714</v>
       </c>
       <c r="O3" s="9">
+        <v>7</v>
+      </c>
+      <c r="P3" s="9">
         <v>6</v>
-      </c>
-      <c r="P3" s="9">
-        <v>5</v>
       </c>
       <c r="Q3" s="9">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="9">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
@@ -813,22 +813,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="9">
-        <v>46101</v>
+        <v>53661</v>
       </c>
       <c r="E4" s="9">
-        <v>3089</v>
+        <v>3597</v>
       </c>
       <c r="F4" s="10">
-        <v>44.772741987698282</v>
+        <v>44.754795663052548</v>
       </c>
       <c r="G4" s="9">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H4" s="9">
         <v>1</v>
@@ -837,25 +837,25 @@
         <v>0</v>
       </c>
       <c r="J4" s="9">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K4" s="9">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="L4" s="9">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M4" s="9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N4" s="11">
-        <v>0.60416666666666663</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="O4" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P4" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="9">
         <v>2</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="9">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
@@ -872,58 +872,58 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="9">
+        <v>54148</v>
+      </c>
+      <c r="E5" s="9">
+        <v>3613</v>
+      </c>
+      <c r="F5" s="10">
+        <v>44.960974259618048</v>
+      </c>
+      <c r="G5" s="9">
+        <v>76</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>112</v>
+      </c>
+      <c r="K5" s="9">
+        <v>66</v>
+      </c>
+      <c r="L5" s="9">
+        <v>46</v>
+      </c>
+      <c r="M5" s="9">
         <v>20</v>
       </c>
-      <c r="D5" s="9">
-        <v>45915</v>
-      </c>
-      <c r="E5" s="9">
-        <v>3031</v>
-      </c>
-      <c r="F5" s="10">
-        <v>45.445397558561531</v>
-      </c>
-      <c r="G5" s="9">
-        <v>44</v>
-      </c>
-      <c r="H5" s="9">
-        <v>2</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>96</v>
-      </c>
-      <c r="K5" s="9">
-        <v>56</v>
-      </c>
-      <c r="L5" s="9">
-        <v>40</v>
-      </c>
-      <c r="M5" s="9">
-        <v>16</v>
-      </c>
       <c r="N5" s="11">
-        <v>0.58333333333333337</v>
+        <v>0.5892857142857143</v>
       </c>
       <c r="O5" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P5" s="9">
         <v>4</v>
       </c>
       <c r="Q5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" s="9">
         <v>1</v>
       </c>
       <c r="S5" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
@@ -931,58 +931,58 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="9">
-        <v>46176</v>
+        <v>61174</v>
       </c>
       <c r="E6" s="9">
-        <v>3109</v>
+        <v>4031</v>
       </c>
       <c r="F6" s="10">
-        <v>44.557092312640719</v>
+        <v>45.527660630116593</v>
       </c>
       <c r="G6" s="9">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H6" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="9">
         <v>0</v>
       </c>
       <c r="J6" s="9">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="K6" s="9">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="L6" s="9">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M6" s="9">
+        <v>14</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0.5546875</v>
+      </c>
+      <c r="O6" s="9">
         <v>8</v>
       </c>
-      <c r="N6" s="11">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="O6" s="9">
-        <v>6</v>
-      </c>
       <c r="P6" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1</v>
+      </c>
+      <c r="R6" s="9">
         <v>3</v>
       </c>
-      <c r="Q6" s="9">
-        <v>2</v>
-      </c>
-      <c r="R6" s="9">
-        <v>1</v>
-      </c>
       <c r="S6" s="9">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
@@ -990,25 +990,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="9">
-        <v>53278</v>
+        <v>53210</v>
       </c>
       <c r="E7" s="9">
-        <v>3502</v>
+        <v>3528</v>
       </c>
       <c r="F7" s="10">
-        <v>45.640776699029132</v>
+        <v>45.246598639455783</v>
       </c>
       <c r="G7" s="9">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="H7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="9">
         <v>0</v>
@@ -1017,31 +1017,31 @@
         <v>112</v>
       </c>
       <c r="K7" s="9">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L7" s="9">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M7" s="9">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N7" s="11">
-        <v>0.5267857142857143</v>
+        <v>0.5625</v>
       </c>
       <c r="O7" s="9">
         <v>7</v>
       </c>
       <c r="P7" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="9">
         <v>1</v>
       </c>
       <c r="R7" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S7" s="9">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
@@ -1049,49 +1049,49 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="9">
-        <v>42619</v>
+        <v>44885</v>
       </c>
       <c r="E8" s="9">
-        <v>3017</v>
+        <v>3043</v>
       </c>
       <c r="F8" s="10">
-        <v>42.378853165396087</v>
+        <v>44.25073940190601</v>
       </c>
       <c r="G8" s="9">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="9">
         <v>0</v>
       </c>
       <c r="J8" s="9">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="K8" s="9">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L8" s="9">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M8" s="9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N8" s="11">
-        <v>0.5267857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="O8" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P8" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="9">
         <v>1</v>
@@ -1100,7 +1100,7 @@
         <v>3</v>
       </c>
       <c r="S8" s="9">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
@@ -1108,10 +1108,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="9">
         <v>53047</v>
@@ -1167,46 +1167,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="9">
-        <v>44885</v>
+        <v>49716</v>
       </c>
       <c r="E10" s="9">
-        <v>3043</v>
+        <v>3477</v>
       </c>
       <c r="F10" s="10">
-        <v>44.25073940190601</v>
+        <v>42.895599654874893</v>
       </c>
       <c r="G10" s="9">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H10" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="9">
         <v>0</v>
       </c>
       <c r="J10" s="9">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="K10" s="9">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="L10" s="9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M10" s="9">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="N10" s="11">
-        <v>0.42857142857142855</v>
+        <v>0.4921875</v>
       </c>
       <c r="O10" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" s="9">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10" s="9">
         <v>10</v>
@@ -1226,22 +1226,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="9">
-        <v>42972</v>
+        <v>49916</v>
       </c>
       <c r="E11" s="9">
-        <v>3013</v>
+        <v>3515</v>
       </c>
       <c r="F11" s="10">
-        <v>42.786591437105869</v>
+        <v>42.602560455192034</v>
       </c>
       <c r="G11" s="9">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1250,22 +1250,22 @@
         <v>0</v>
       </c>
       <c r="J11" s="9">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K11" s="9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L11" s="9">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="M11" s="9">
-        <v>-10</v>
+        <v>-22</v>
       </c>
       <c r="N11" s="11">
-        <v>0.44791666666666669</v>
+        <v>0.4017857142857143</v>
       </c>
       <c r="O11" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P11" s="9">
         <v>2</v>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S11" s="9">
         <v>6</v>
@@ -1285,22 +1285,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="9">
-        <v>53052</v>
+        <v>60039</v>
       </c>
       <c r="E12" s="9">
-        <v>3578</v>
+        <v>4004</v>
       </c>
       <c r="F12" s="10">
-        <v>44.481833426495243</v>
+        <v>44.984265734265733</v>
       </c>
       <c r="G12" s="9">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H12" s="9">
         <v>2</v>
@@ -1309,22 +1309,22 @@
         <v>0</v>
       </c>
       <c r="J12" s="9">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="K12" s="9">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L12" s="9">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="M12" s="9">
-        <v>-14</v>
+        <v>-20</v>
       </c>
       <c r="N12" s="11">
-        <v>0.4375</v>
+        <v>0.421875</v>
       </c>
       <c r="O12" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P12" s="9">
         <v>1</v>
@@ -1333,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="R12" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S12" s="9">
         <v>4</v>
@@ -1344,22 +1344,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="9">
-        <v>50774</v>
+        <v>57839</v>
       </c>
       <c r="E13" s="9">
-        <v>3639</v>
+        <v>4169</v>
       </c>
       <c r="F13" s="10">
-        <v>41.858202802967853</v>
+        <v>41.620772367474217</v>
       </c>
       <c r="G13" s="9">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1368,22 +1368,22 @@
         <v>0</v>
       </c>
       <c r="J13" s="9">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="K13" s="9">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L13" s="9">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="M13" s="9">
-        <v>-38</v>
+        <v>-46</v>
       </c>
       <c r="N13" s="11">
-        <v>0.33035714285714285</v>
+        <v>0.3203125</v>
       </c>
       <c r="O13" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P13" s="9">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S13" s="9">
         <v>0</v>
@@ -1403,10 +1403,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="9">
         <v>43453</v>
@@ -1427,22 +1427,22 @@
         <v>0</v>
       </c>
       <c r="J14" s="9">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K14" s="9">
         <v>26</v>
       </c>
       <c r="L14" s="9">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="M14" s="9">
-        <v>-44</v>
+        <v>-60</v>
       </c>
       <c r="N14" s="11">
-        <v>0.27083333333333331</v>
+        <v>0.23214285714285715</v>
       </c>
       <c r="O14" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P14" s="9">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S14" s="9">
         <v>0</v>
